--- a/assets/libreoffice_calc_njc/6e50aca3-551a-4948-83a2-ae8a1c5c4867/QtrFullYear_L3_10.xlsx
+++ b/assets/libreoffice_calc_njc/6e50aca3-551a-4948-83a2-ae8a1c5c4867/QtrFullYear_L3_10.xlsx
@@ -107,7 +107,7 @@
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -129,14 +129,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -186,11 +178,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -202,7 +194,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -215,6 +207,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF3D3D3D"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -224,7 +233,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -271,222 +280,222 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>220000</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>250000</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>280000</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>130000</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>9500</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>460000</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>490000</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0.516</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>150000</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>165000</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>125000</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>180000</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>140000</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>695000</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>515000</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>180000</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>0.259</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>80000</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>375000</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>270000</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>105000</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>85000</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>460000</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>3700</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>90000</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0.196</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>32000</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>26000</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>28000</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>38000</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <v>135000</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>109000</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>26000</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0.193</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -548,7 +557,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -568,7 +577,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="4" t="n">
@@ -585,7 +594,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="4" t="n">
@@ -602,7 +611,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="4" t="n">
@@ -619,7 +628,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="4" t="n">
@@ -636,7 +645,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="4" t="n">

--- a/assets/libreoffice_calc_njc/6e50aca3-551a-4948-83a2-ae8a1c5c4867/QtrFullYear_L3_10.xlsx
+++ b/assets/libreoffice_calc_njc/6e50aca3-551a-4948-83a2-ae8a1c5c4867/QtrFullYear_L3_10.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Q1-Q4" sheetId="1" state="visible" r:id="rId2"/>
@@ -107,7 +107,7 @@
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -130,6 +130,14 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -173,19 +181,23 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -194,7 +206,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -207,23 +219,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF3D3D3D"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -280,222 +275,222 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>200000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>220000</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="3" t="n">
         <v>110000</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="3" t="n">
         <v>250000</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="3" t="n">
         <v>120000</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="3" t="n">
         <v>280000</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="3" t="n">
         <v>130000</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>9500</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="3" t="n">
         <v>460000</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="3" t="n">
         <v>490000</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="5" t="n">
         <v>0.516</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>150000</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="3" t="n">
         <v>120000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="3" t="n">
         <v>165000</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="3" t="n">
         <v>125000</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="3" t="n">
         <v>180000</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="3" t="n">
         <v>130000</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="3" t="n">
         <v>200000</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="3" t="n">
         <v>140000</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="3" t="n">
         <v>695000</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="3" t="n">
         <v>515000</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="3" t="n">
         <v>180000</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="5" t="n">
         <v>0.259</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>80000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="3" t="n">
         <v>60000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="3" t="n">
         <v>90000</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="3" t="n">
         <v>65000</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="3" t="n">
         <v>95000</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="3" t="n">
         <v>110000</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="3" t="n">
         <v>75000</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="3" t="n">
         <v>375000</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="3" t="n">
         <v>270000</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="3" t="n">
         <v>105000</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="3" t="n">
         <v>85000</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="3" t="n">
         <v>110000</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="3" t="n">
         <v>90000</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="3" t="n">
         <v>120000</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="3" t="n">
         <v>95000</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="3" t="n">
         <v>130000</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="3" t="n">
         <v>460000</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <v>3700</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="3" t="n">
         <v>90000</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.196</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="3" t="n">
         <v>25000</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="3" t="n">
         <v>32000</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="3" t="n">
         <v>26000</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="3" t="n">
         <v>35000</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="3" t="n">
         <v>28000</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="3" t="n">
         <v>38000</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="3" t="n">
         <v>135000</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="3" t="n">
         <v>109000</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="3" t="n">
         <v>26000</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="5" t="n">
         <v>0.193</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -536,7 +531,7 @@
       <c r="L7" s="1" t="n">
         <v>891000</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="6" t="n">
         <v>0.341</v>
       </c>
     </row>
@@ -557,107 +552,107 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>0.136</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>0.091</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>0.111</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>0.056</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.158</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>0.091</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.083</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>0.067</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>0.094</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.086</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.267</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/6e50aca3-551a-4948-83a2-ae8a1c5c4867/QtrFullYear_L3_10.xlsx
+++ b/assets/libreoffice_calc_njc/6e50aca3-551a-4948-83a2-ae8a1c5c4867/QtrFullYear_L3_10.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Q1-Q4" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t xml:space="preserve">Department</t>
   </si>
@@ -50,21 +50,21 @@
     <t xml:space="preserve">Q4 Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Annual Revenue</t>
+    <t xml:space="preserve">Annual RevenueAnnual CoAnnual Margin %PrRevenue Rankofitst</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Annual Profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin %</t>
+    <t xml:space="preserve">Annual ProfitMargin %</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue Rank</t>
   </si>
   <si>
+    <t xml:space="preserve">Operations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sales</t>
   </si>
   <si>
@@ -74,28 +74,22 @@
     <t xml:space="preserve">Marketing</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0%%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations</t>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1-Q2 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2-Q3 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3-Q4 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Year Growth %</t>
   </si>
   <si>
     <t xml:space="preserve">HR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1-Q2 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q2-Q3 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3-Q4 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full Year Growth %</t>
   </si>
 </sst>
 </file>
@@ -181,8 +175,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -194,19 +196,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -227,8 +217,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ7"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="13.34"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -264,276 +259,265 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="AMG1" s="0"/>
+      <c r="AMH1" s="0"/>
+      <c r="AMI1" s="0"/>
+      <c r="AMJ1" s="0"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="1" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>95000</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>460000</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <f aca="false">C2+E2+G2+IH32</f>
+        <v>270000</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <f aca="false">J2-K2</f>
+        <v>190000</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <f aca="false">L3/J3*100</f>
+        <v>51.5789473684211</v>
+      </c>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C3" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D3" s="1" t="n">
         <v>220000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E3" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F3" s="1" t="n">
         <v>250000</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G3" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H3" s="1" t="n">
         <v>280000</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I3" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>9500</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="J3" s="2" t="n">
+        <f aca="false">B3+D3+F3+H3</f>
+        <v>950000</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <f aca="false">C3+E3+G3+I3</f>
         <v>460000</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L3" s="2" t="n">
+        <f aca="false">J3-K3</f>
         <v>490000</v>
       </c>
-      <c r="M2" s="5" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="M3" s="2" t="n">
+        <f aca="false">L3/J3*100</f>
+        <v>51.5789473684211</v>
+      </c>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="1" t="n">
         <v>150000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D4" s="1" t="n">
         <v>165000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E4" s="1" t="n">
         <v>125000</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F4" s="1" t="n">
         <v>180000</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G4" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H4" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I4" s="1" t="n">
         <v>140000</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="1" t="n">
         <v>695000</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>515000</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>180000</v>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B5" s="1" t="n">
         <v>80000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C5" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D5" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E5" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F5" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G5" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H5" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I5" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J5" s="1" t="n">
         <v>375000</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>270000</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>105000</v>
-      </c>
-      <c r="M4" s="5" t="s">
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>85000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>110000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>95000</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>460000</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>3700</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>90000</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>38000</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>135000</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>109000</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>26000</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="B6" s="1" t="n">
+        <v>560000</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>390000</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>617000</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>416000</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>680000</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>443000</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>758000</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>475000</v>
+      </c>
+      <c r="J6" s="1" t="e">
+        <f aca="false">SUM(B6:E6)#REF!=J2-#REF!=J2-#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>560000</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>390000</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>617000</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>416000</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>680000</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>443000</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>758000</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>475000</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>2615000</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>1724000</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>891000</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0.341</v>
-      </c>
+      <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <f aca="false">SUM(B2:B6)</f>
+        <v>1090000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <f aca="false">SUM(C2:C6)</f>
+        <v>755000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <f aca="false">SUM(D2:D6)</f>
+        <v>1202000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <f aca="false">SUM(E2:E6)</f>
+        <v>806000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <f aca="false">SUM(F2:F6)</f>
+        <v>1325000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <f aca="false">SUM(G2:G6)</f>
+        <v>858000</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <f aca="false">SUM(H2:H6)</f>
+        <v>1478000</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <f aca="false">SUM(I2:I6)</f>
+        <v>920000</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <f aca="false">SUM(B7:H7)</f>
+        <v>7514000</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="AMG7" s="0"/>
+      <c r="AMH7" s="0"/>
+      <c r="AMI7" s="0"/>
+      <c r="AMJ7" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -552,27 +536,27 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="5" t="n">
@@ -589,7 +573,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="5" t="n">
@@ -606,7 +590,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="5" t="n">
@@ -623,8 +607,8 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
+      <c r="A5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>0.1</v>
@@ -640,8 +624,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
+      <c r="A6" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>0.067</v>
